--- a/crates/xlstream-eval/tests/fixtures/statistical/norm_s_dist.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/statistical/norm_s_dist.xlsx
@@ -1,116 +1,123 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2B59D2BFD3905C4F6943D5F050D8A033557FFB8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t xml:space="preserve">z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDF z=0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDF z=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDF z=-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDF z=1.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDF z=-1.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDF z=3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDF z=0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDF z=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDF z=-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INV median</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INV upper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INV lower</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INV ~1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INV far tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">round-trip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nested ROUND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nested IF</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>CDF z=0</t>
+  </si>
+  <si>
+    <t>CDF z=1</t>
+  </si>
+  <si>
+    <t>CDF z=-1</t>
+  </si>
+  <si>
+    <t>CDF z=1.96</t>
+  </si>
+  <si>
+    <t>CDF z=-1.96</t>
+  </si>
+  <si>
+    <t>CDF z=3</t>
+  </si>
+  <si>
+    <t>PDF z=0</t>
+  </si>
+  <si>
+    <t>PDF z=1</t>
+  </si>
+  <si>
+    <t>PDF z=-1</t>
+  </si>
+  <si>
+    <t>INV median</t>
+  </si>
+  <si>
+    <t>INV upper</t>
+  </si>
+  <si>
+    <t>INV lower</t>
+  </si>
+  <si>
+    <t>INV ~1</t>
+  </si>
+  <si>
+    <t>INV far tail</t>
+  </si>
+  <si>
+    <t>round-trip</t>
+  </si>
+  <si>
+    <t>nested ROUND</t>
+  </si>
+  <si>
+    <t>nested IF</t>
+  </si>
+  <si>
+    <t>p=0 NUM</t>
+  </si>
+  <si>
+    <t>p=1 NUM</t>
+  </si>
+  <si>
+    <t>p&lt;0 NUM</t>
+  </si>
+  <si>
+    <t>p&gt;1 NUM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,7 +129,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -130,57 +137,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -215,338 +202,473 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>-3</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(0,TRUE())</f>
+      <c r="C2">
+        <f>_xlfn.NORM.S.DIST(0,TRUE)</f>
         <v>0.5</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>-2</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(1,TRUE())</f>
-        <v>0.841344746068543</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3">
+        <f>_xlfn.NORM.S.DIST(1,TRUE)</f>
+        <v>0.84134474606854304</v>
+      </c>
+      <c r="D3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>-1</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(-1,TRUE())</f>
-        <v>0.158655253931457</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4">
+        <f>_xlfn.NORM.S.DIST(-1,TRUE)</f>
+        <v>0.15865525393145699</v>
+      </c>
+      <c r="D4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>0</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(1.96,TRUE())</f>
-        <v>0.97500210485178</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5">
+        <f>_xlfn.NORM.S.DIST(1.96,TRUE)</f>
+        <v>0.97500210485177952</v>
+      </c>
+      <c r="D5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(-1.96,TRUE())</f>
-        <v>0.0249978951482204</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6">
+        <f>_xlfn.NORM.S.DIST(-1.96,TRUE)</f>
+        <v>2.4997895148220432E-2</v>
+      </c>
+      <c r="D6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>2</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(3,TRUE())</f>
-        <v>0.99865010196837</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7">
+        <f>_xlfn.NORM.S.DIST(3,TRUE)</f>
+        <v>0.9986501019683699</v>
+      </c>
+      <c r="D7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>3</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(0,FALSE())</f>
-        <v>0.398942280401433</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8">
+        <f>_xlfn.NORM.S.DIST(0,FALSE)</f>
+        <v>0.3989422804014327</v>
+      </c>
+      <c r="D8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(1,FALSE())</f>
-        <v>0.241970724519143</v>
-      </c>
-      <c r="D9" s="0" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C9">
+        <f>_xlfn.NORM.S.DIST(1,FALSE)</f>
+        <v>0.24197072451914337</v>
+      </c>
+      <c r="D9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.DIST(-1,FALSE())</f>
-        <v>0.241970724519143</v>
-      </c>
-      <c r="D10" s="0" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C10">
+        <f>_xlfn.NORM.S.DIST(-1,FALSE)</f>
+        <v>0.24197072451914337</v>
+      </c>
+      <c r="D10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.INV(0.5)</f>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C11">
+        <f>_xlfn.NORM.S.INV(0.5)</f>
         <v>0</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.INV(0.975)</f>
-        <v>1.95996398454005</v>
-      </c>
-      <c r="D12" s="0" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C12">
+        <f>_xlfn.NORM.S.INV(0.975)</f>
+        <v>1.9599639845400536</v>
+      </c>
+      <c r="D12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.INV(0.025)</f>
-        <v>-1.95996398454005</v>
-      </c>
-      <c r="D13" s="0" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C13">
+        <f>_xlfn.NORM.S.INV(0.025)</f>
+        <v>-1.9599639845400538</v>
+      </c>
+      <c r="D13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.INV(0.841345)</f>
-        <v>1.00000104943105</v>
-      </c>
-      <c r="D14" s="0" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C14">
+        <f>_xlfn.NORM.S.INV(0.841345)</f>
+        <v>1.000001049431047</v>
+      </c>
+      <c r="D14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.INV(0.001)</f>
-        <v>-3.09023230616781</v>
-      </c>
-      <c r="D15" s="0" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C15">
+        <f>_xlfn.NORM.S.INV(0.001)</f>
+        <v>-3.0902323061678132</v>
+      </c>
+      <c r="D15" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="0" t="n">
-        <f aca="false">_xlfn.NORM.S.INV(_xlfn.NORM.S.DIST(1.5,TRUE()))</f>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C16">
+        <f>_xlfn.NORM.S.INV(_xlfn.NORM.S.DIST(1.5,TRUE))</f>
         <v>1.5</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="0" t="n">
-        <f aca="false">ROUND(_xlfn.NORM.S.DIST(0,TRUE()),1)</f>
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C17">
+        <f>ROUND(_xlfn.NORM.S.DIST(0,TRUE),1)</f>
         <v>0.5</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="0" t="str">
-        <f aca="false">IF(_xlfn.NORM.S.DIST(2,TRUE())&gt;0.95,"sig","ns")</f>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C18" t="str">
+        <f>IF(_xlfn.NORM.S.DIST(2,TRUE)&gt;0.95,"sig","ns")</f>
         <v>sig</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" t="s">
         <v>19</v>
       </c>
     </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C19" t="e">
+        <f>_xlfn.NORM.S.INV(0)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C20" t="e">
+        <f>_xlfn.NORM.S.INV(1)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C21" t="e">
+        <f>_xlfn.NORM.S.INV(-0.5)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="C22" t="e">
+        <f>_xlfn.NORM.S.INV(1.5)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>